--- a/en/downloads/data-excel/4.4.1.1.xlsx
+++ b/en/downloads/data-excel/4.4.1.1.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Национальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Национальные показатели ЦУР — 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2690DC9-D343-4AD5-BE8A-6DD633B64713}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -80,15 +81,6 @@
     <t>The number of students studying in the field of ICT at the level of higher professional education</t>
   </si>
   <si>
-    <t>4.4.1.1а Численность студентов (в разбивке по полу), обучающихся по направлению ИКТ в системе начального профессионального, среднего профессионального и высшего профессиональног образования</t>
-  </si>
-  <si>
-    <t>4.4.1.1a The number of students (disaggregated by sex) studying in the field of ICT in the system of primary vocational, secondary vocational and higher professional education</t>
-  </si>
-  <si>
-    <t>4.4.1.1а МКТ багыты боюнча системасынын баштапкы кесиптик, орто кесиптик жана жогорку кесиптик билим берүүчү жакта окуган студенттердин саны (жынынсы боюнча бөлүнгөн)</t>
-  </si>
-  <si>
     <t>(число)</t>
   </si>
   <si>
@@ -96,12 +88,21 @@
   </si>
   <si>
     <t>(number)</t>
+  </si>
+  <si>
+    <t>4.4.1.1 The number of students (disaggregated by sex) studying in the field of ICT in the system of primary vocational, secondary vocational and higher professional education</t>
+  </si>
+  <si>
+    <t>4.4.1.1 Численность студентов (в разбивке по полу), обучающихся по направлению ИКТ в системе начального профессионального, среднего профессионального и высшего профессиональног образования</t>
+  </si>
+  <si>
+    <t>4.4.1.1 МКТ багыты боюнча системасынын баштапкы кесиптик, орто кесиптик жана жогорку кесиптик билим берүүчү жакта окуган студенттердин саны (жынынсы боюнча бөлүнгөн)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -182,7 +183,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -208,10 +209,7 @@
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -230,12 +228,14 @@
     <xf numFmtId="3" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -515,8 +515,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O16"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:P12"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="39.28515625" style="2" customWidth="1"/>
@@ -524,29 +524,29 @@
     <col min="4" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="66" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:15" s="10" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="17" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3"/>
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
@@ -562,15 +562,16 @@
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
-    </row>
-    <row r="4" spans="1:15" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="11" t="s">
+      <c r="P3" s="18"/>
+    </row>
+    <row r="4" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="12" t="s">
+      <c r="C4" s="11" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="5">
@@ -597,20 +598,23 @@
       <c r="K4" s="5">
         <v>2019</v>
       </c>
-      <c r="L4" s="13">
+      <c r="L4" s="12">
         <v>2020</v>
       </c>
-      <c r="M4" s="13">
+      <c r="M4" s="12">
         <v>2021</v>
       </c>
-      <c r="N4" s="13">
+      <c r="N4" s="12">
         <v>2022</v>
       </c>
-      <c r="O4" s="13">
+      <c r="O4" s="12">
         <v>2023</v>
       </c>
-    </row>
-    <row r="5" spans="1:15" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P4" s="19">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="42" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="6" t="s">
         <v>8</v>
       </c>
@@ -644,20 +648,23 @@
       <c r="K5" s="2">
         <v>911</v>
       </c>
-      <c r="L5" s="14">
+      <c r="L5" s="13">
         <v>1004</v>
       </c>
-      <c r="M5" s="14">
+      <c r="M5" s="13">
         <v>952</v>
       </c>
-      <c r="N5" s="14">
+      <c r="N5" s="13">
         <v>1434</v>
       </c>
-      <c r="O5" s="14">
+      <c r="O5" s="13">
         <v>1731</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P5" s="13">
+        <v>2947</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
@@ -691,20 +698,23 @@
       <c r="K6" s="2">
         <v>6794</v>
       </c>
-      <c r="L6" s="14">
+      <c r="L6" s="13">
         <v>8279</v>
       </c>
-      <c r="M6" s="14">
+      <c r="M6" s="13">
         <v>10437</v>
       </c>
-      <c r="N6" s="14">
+      <c r="N6" s="13">
         <v>12822</v>
       </c>
-      <c r="O6" s="14">
+      <c r="O6" s="13">
         <v>15467</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P6" s="13">
+        <v>17040</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -738,20 +748,23 @@
       <c r="K7" s="2">
         <v>1675</v>
       </c>
-      <c r="L7" s="14">
+      <c r="L7" s="13">
         <v>1752</v>
       </c>
-      <c r="M7" s="14">
+      <c r="M7" s="13">
         <v>2253</v>
       </c>
-      <c r="N7" s="14">
+      <c r="N7" s="13">
         <v>3099</v>
       </c>
-      <c r="O7" s="14">
+      <c r="O7" s="13">
         <v>3820</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P7" s="13">
+        <v>4195</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>11</v>
       </c>
@@ -785,20 +798,23 @@
       <c r="K8" s="2">
         <v>5119</v>
       </c>
-      <c r="L8" s="14">
+      <c r="L8" s="13">
         <v>6527</v>
       </c>
-      <c r="M8" s="14">
+      <c r="M8" s="13">
         <v>8184</v>
       </c>
-      <c r="N8" s="14">
+      <c r="N8" s="13">
         <v>9722</v>
       </c>
-      <c r="O8" s="14">
+      <c r="O8" s="13">
         <v>11647</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P8" s="13">
+        <v>12845</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
         <v>12</v>
       </c>
@@ -832,20 +848,23 @@
       <c r="K9" s="7">
         <v>9511</v>
       </c>
-      <c r="L9" s="15">
+      <c r="L9" s="14">
         <v>10324</v>
       </c>
-      <c r="M9" s="15">
+      <c r="M9" s="14">
         <v>14020</v>
       </c>
-      <c r="N9" s="15">
+      <c r="N9" s="14">
         <v>14424</v>
       </c>
-      <c r="O9" s="15">
+      <c r="O9" s="14">
         <v>16267</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="P9" s="14">
+        <v>16318</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>10</v>
       </c>
@@ -879,20 +898,23 @@
       <c r="K10" s="7">
         <v>3982</v>
       </c>
-      <c r="L10" s="15">
+      <c r="L10" s="14">
         <v>4131</v>
       </c>
-      <c r="M10" s="15">
+      <c r="M10" s="14">
         <v>5139</v>
       </c>
-      <c r="N10" s="15">
+      <c r="N10" s="14">
         <v>5279</v>
       </c>
-      <c r="O10" s="15">
+      <c r="O10" s="14">
         <v>5513</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="P10" s="14">
+        <v>5931</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="3" t="s">
         <v>11</v>
       </c>
@@ -926,33 +948,24 @@
       <c r="K11" s="8">
         <v>5529</v>
       </c>
-      <c r="L11" s="16">
+      <c r="L11" s="15">
         <v>6193</v>
       </c>
-      <c r="M11" s="16">
+      <c r="M11" s="15">
         <v>8881</v>
       </c>
-      <c r="N11" s="16">
+      <c r="N11" s="15">
         <v>9145</v>
       </c>
-      <c r="O11" s="16">
+      <c r="O11" s="15">
         <v>10754</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="P11" s="15">
+        <v>10387</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="M12" s="9"/>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="M13" s="10"/>
-    </row>
-    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="M14" s="10"/>
-    </row>
-    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="M15" s="10"/>
-    </row>
-    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="M16" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
